--- a/04_Figures/F04_association/modules/T1/limma/c_data/results.xlsx
+++ b/04_Figures/F04_association/modules/T1/limma/c_data/results.xlsx
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="37" uniqueCount="37">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="35" uniqueCount="35">
   <si>
     <t xml:space="preserve">outcome</t>
   </si>
@@ -70,12 +70,6 @@
   </si>
   <si>
     <t xml:space="preserve">ME_red</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ME_salmon</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ME_tan</t>
   </si>
   <si>
     <t xml:space="preserve">ME_turquoise</t>
@@ -492,16 +486,16 @@
         <v>8</v>
       </c>
       <c r="D2" t="n">
-        <v>0.00387674595299995</v>
+        <v>-0.000886339950601966</v>
       </c>
       <c r="E2" t="n">
-        <v>0.757100295243685</v>
+        <v>-0.184576545954381</v>
       </c>
       <c r="F2" t="n">
-        <v>0.455585691374905</v>
+        <v>0.854950371586535</v>
       </c>
       <c r="G2" t="n">
-        <v>0.826837598280106</v>
+        <v>0.895857924068251</v>
       </c>
     </row>
     <row r="3">
@@ -515,16 +509,16 @@
         <v>9</v>
       </c>
       <c r="D3" t="n">
-        <v>-0.000894872538220485</v>
+        <v>0.00285792828178187</v>
       </c>
       <c r="E3" t="n">
-        <v>-0.202272271617933</v>
+        <v>0.76413889242099</v>
       </c>
       <c r="F3" t="n">
-        <v>0.841229392164457</v>
+        <v>0.451458118154545</v>
       </c>
       <c r="G3" t="n">
-        <v>0.898032721780164</v>
+        <v>0.890287556614687</v>
       </c>
     </row>
     <row r="4">
@@ -538,16 +532,16 @@
         <v>10</v>
       </c>
       <c r="D4" t="n">
-        <v>-0.0040987636447643</v>
+        <v>0.00069315229732771</v>
       </c>
       <c r="E4" t="n">
-        <v>-0.986814719583717</v>
+        <v>0.145918177824921</v>
       </c>
       <c r="F4" t="n">
-        <v>0.332547117129187</v>
+        <v>0.885077641881572</v>
       </c>
       <c r="G4" t="n">
-        <v>0.826837598280106</v>
+        <v>0.895857924068251</v>
       </c>
     </row>
     <row r="5">
@@ -561,16 +555,16 @@
         <v>11</v>
       </c>
       <c r="D5" t="n">
-        <v>0.00219214831707933</v>
+        <v>0.000691974554446806</v>
       </c>
       <c r="E5" t="n">
-        <v>0.628803512294913</v>
+        <v>0.132143073444698</v>
       </c>
       <c r="F5" t="n">
-        <v>0.534793431982543</v>
+        <v>0.895857924068251</v>
       </c>
       <c r="G5" t="n">
-        <v>0.826837598280106</v>
+        <v>0.895857924068251</v>
       </c>
     </row>
     <row r="6">
@@ -584,16 +578,16 @@
         <v>12</v>
       </c>
       <c r="D6" t="n">
-        <v>-0.0045405101090101</v>
+        <v>-0.00512364893834896</v>
       </c>
       <c r="E6" t="n">
-        <v>-0.961046712656083</v>
+        <v>-1.05767372136612</v>
       </c>
       <c r="F6" t="n">
-        <v>0.345107926777311</v>
+        <v>0.299642046679561</v>
       </c>
       <c r="G6" t="n">
-        <v>0.826837598280106</v>
+        <v>0.890287556614687</v>
       </c>
     </row>
     <row r="7">
@@ -607,16 +601,16 @@
         <v>13</v>
       </c>
       <c r="D7" t="n">
-        <v>0.00751585851897383</v>
+        <v>0.00368148916487229</v>
       </c>
       <c r="E7" t="n">
-        <v>1.60456714657648</v>
+        <v>0.698745485474325</v>
       </c>
       <c r="F7" t="n">
-        <v>0.120293777118782</v>
+        <v>0.49072894042236</v>
       </c>
       <c r="G7" t="n">
-        <v>0.826837598280106</v>
+        <v>0.890287556614687</v>
       </c>
     </row>
     <row r="8">
@@ -630,16 +624,16 @@
         <v>14</v>
       </c>
       <c r="D8" t="n">
-        <v>0.00183700012443029</v>
+        <v>0.00262746819273299</v>
       </c>
       <c r="E8" t="n">
-        <v>0.388776507167705</v>
+        <v>0.588716733342638</v>
       </c>
       <c r="F8" t="n">
-        <v>0.700508823194286</v>
+        <v>0.560979364819908</v>
       </c>
       <c r="G8" t="n">
-        <v>0.898032721780164</v>
+        <v>0.890287556614687</v>
       </c>
     </row>
     <row r="9">
@@ -653,16 +647,16 @@
         <v>15</v>
       </c>
       <c r="D9" t="n">
-        <v>0.00102086780506848</v>
+        <v>0.00241531263746624</v>
       </c>
       <c r="E9" t="n">
-        <v>0.227241890804329</v>
+        <v>0.46246177496039</v>
       </c>
       <c r="F9" t="n">
-        <v>0.821957821383484</v>
+        <v>0.647481859356136</v>
       </c>
       <c r="G9" t="n">
-        <v>0.898032721780164</v>
+        <v>0.890287556614687</v>
       </c>
     </row>
     <row r="10">
@@ -676,16 +670,16 @@
         <v>16</v>
       </c>
       <c r="D10" t="n">
-        <v>0.000661371450737145</v>
+        <v>0.00326770299360769</v>
       </c>
       <c r="E10" t="n">
-        <v>0.129365999129591</v>
+        <v>0.585027817994201</v>
       </c>
       <c r="F10" t="n">
-        <v>0.898032721780164</v>
+        <v>0.563421132313664</v>
       </c>
       <c r="G10" t="n">
-        <v>0.898032721780164</v>
+        <v>0.890287556614687</v>
       </c>
     </row>
     <row r="11">
@@ -699,16 +693,16 @@
         <v>17</v>
       </c>
       <c r="D11" t="n">
-        <v>0.00397880068141914</v>
+        <v>-0.00247042751036466</v>
       </c>
       <c r="E11" t="n">
-        <v>0.988756953530334</v>
+        <v>-0.50840342924718</v>
       </c>
       <c r="F11" t="n">
-        <v>0.331613157587991</v>
+        <v>0.615328805838308</v>
       </c>
       <c r="G11" t="n">
-        <v>0.826837598280106</v>
+        <v>0.890287556614687</v>
       </c>
     </row>
     <row r="12">
@@ -722,62 +716,16 @@
         <v>18</v>
       </c>
       <c r="D12" t="n">
-        <v>0.00457255139788549</v>
+        <v>-0.00402126364018482</v>
       </c>
       <c r="E12" t="n">
-        <v>1.14386188108418</v>
+        <v>-0.92576947262145</v>
       </c>
       <c r="F12" t="n">
-        <v>0.262781253728913</v>
+        <v>0.362825107404075</v>
       </c>
       <c r="G12" t="n">
-        <v>0.826837598280106</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="s">
-        <v>7</v>
-      </c>
-      <c r="B13" t="n">
-        <v>15</v>
-      </c>
-      <c r="C13" t="s">
-        <v>19</v>
-      </c>
-      <c r="D13" t="n">
-        <v>-0.00269110427081821</v>
-      </c>
-      <c r="E13" t="n">
-        <v>-0.571755426530525</v>
-      </c>
-      <c r="F13" t="n">
-        <v>0.5722457591863</v>
-      </c>
-      <c r="G13" t="n">
-        <v>0.826837598280106</v>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="s">
-        <v>7</v>
-      </c>
-      <c r="B14" t="n">
-        <v>15</v>
-      </c>
-      <c r="C14" t="s">
-        <v>20</v>
-      </c>
-      <c r="D14" t="n">
-        <v>0.00290840880033159</v>
-      </c>
-      <c r="E14" t="n">
-        <v>0.571485540068706</v>
-      </c>
-      <c r="F14" t="n">
-        <v>0.572426029578535</v>
-      </c>
-      <c r="G14" t="n">
-        <v>0.826837598280106</v>
+        <v>0.890287556614687</v>
       </c>
     </row>
   </sheetData>
@@ -816,7 +764,7 @@
     </row>
     <row r="2">
       <c r="A2" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="B2" t="n">
         <v>15</v>
@@ -825,21 +773,21 @@
         <v>8</v>
       </c>
       <c r="D2" t="n">
-        <v>0.0000292855094056211</v>
+        <v>0.00000649927619692228</v>
       </c>
       <c r="E2" t="n">
-        <v>0.95992703587386</v>
+        <v>0.224427121217985</v>
       </c>
       <c r="F2" t="n">
-        <v>0.345182039964619</v>
+        <v>0.824056581469828</v>
       </c>
       <c r="G2" t="n">
-        <v>0.795780330091566</v>
+        <v>0.937450214295248</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="B3" t="n">
         <v>15</v>
@@ -848,21 +796,21 @@
         <v>9</v>
       </c>
       <c r="D3" t="n">
-        <v>-0.00000733298068643751</v>
+        <v>0.00000894565909042601</v>
       </c>
       <c r="E3" t="n">
-        <v>-0.274715710549826</v>
+        <v>0.388420257369942</v>
       </c>
       <c r="F3" t="n">
-        <v>0.785520380673548</v>
+        <v>0.700646290361931</v>
       </c>
       <c r="G3" t="n">
-        <v>0.898701544885374</v>
+        <v>0.937450214295248</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="B4" t="n">
         <v>15</v>
@@ -871,21 +819,21 @@
         <v>10</v>
       </c>
       <c r="D4" t="n">
-        <v>-0.0000338771870895081</v>
+        <v>-0.00000538860207142132</v>
       </c>
       <c r="E4" t="n">
-        <v>-1.36625859559032</v>
+        <v>-0.188008558179648</v>
       </c>
       <c r="F4" t="n">
-        <v>0.182563727240843</v>
+        <v>0.852227467541134</v>
       </c>
       <c r="G4" t="n">
-        <v>0.795780330091566</v>
+        <v>0.937450214295248</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="B5" t="n">
         <v>15</v>
@@ -894,21 +842,21 @@
         <v>11</v>
       </c>
       <c r="D5" t="n">
-        <v>0.00000486623732616084</v>
+        <v>-0.0000162636307463881</v>
       </c>
       <c r="E5" t="n">
-        <v>0.225932132732395</v>
+        <v>-0.5188644665199</v>
       </c>
       <c r="F5" t="n">
-        <v>0.822869969528695</v>
+        <v>0.607937037298076</v>
       </c>
       <c r="G5" t="n">
-        <v>0.898701544885374</v>
+        <v>0.937450214295248</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="B6" t="n">
         <v>15</v>
@@ -917,21 +865,21 @@
         <v>12</v>
       </c>
       <c r="D6" t="n">
-        <v>-0.0000025228192156959</v>
+        <v>-0.0000063129004003001</v>
       </c>
       <c r="E6" t="n">
-        <v>-0.0873613053683252</v>
+        <v>-0.212075196571105</v>
       </c>
       <c r="F6" t="n">
-        <v>0.930996516332711</v>
+        <v>0.833586437396414</v>
       </c>
       <c r="G6" t="n">
-        <v>0.930996516332711</v>
+        <v>0.937450214295248</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="B7" t="n">
         <v>15</v>
@@ -940,21 +888,21 @@
         <v>13</v>
       </c>
       <c r="D7" t="n">
-        <v>0.0000476718735692003</v>
+        <v>0.0000289167442280378</v>
       </c>
       <c r="E7" t="n">
-        <v>1.69924017717952</v>
+        <v>0.918641403816328</v>
       </c>
       <c r="F7" t="n">
-        <v>0.100188136312017</v>
+        <v>0.366138690575127</v>
       </c>
       <c r="G7" t="n">
-        <v>0.795780330091566</v>
+        <v>0.937450214295248</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="B8" t="n">
         <v>15</v>
@@ -963,21 +911,21 @@
         <v>14</v>
       </c>
       <c r="D8" t="n">
-        <v>0.000025734110587768</v>
+        <v>0.0000322014075529192</v>
       </c>
       <c r="E8" t="n">
-        <v>0.916165858841807</v>
+        <v>1.21582185858851</v>
       </c>
       <c r="F8" t="n">
-        <v>0.367283229273031</v>
+        <v>0.234216334089953</v>
       </c>
       <c r="G8" t="n">
-        <v>0.795780330091566</v>
+        <v>0.937450214295248</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="B9" t="n">
         <v>15</v>
@@ -986,21 +934,21 @@
         <v>15</v>
       </c>
       <c r="D9" t="n">
-        <v>0.0000268320312948961</v>
+        <v>0.0000231063867729509</v>
       </c>
       <c r="E9" t="n">
-        <v>1.00675783566147</v>
+        <v>0.740080748536924</v>
       </c>
       <c r="F9" t="n">
-        <v>0.32254009854047</v>
+        <v>0.4654189743161</v>
       </c>
       <c r="G9" t="n">
-        <v>0.795780330091566</v>
+        <v>0.937450214295248</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="B10" t="n">
         <v>15</v>
@@ -1009,21 +957,21 @@
         <v>16</v>
       </c>
       <c r="D10" t="n">
-        <v>-0.000017230061084906</v>
+        <v>0.000000588047881960782</v>
       </c>
       <c r="E10" t="n">
-        <v>-0.565319870624619</v>
+        <v>0.0174396324353364</v>
       </c>
       <c r="F10" t="n">
-        <v>0.576289020859812</v>
+        <v>0.986209717364775</v>
       </c>
       <c r="G10" t="n">
-        <v>0.898701544885374</v>
+        <v>0.986209717364775</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="B11" t="n">
         <v>15</v>
@@ -1032,21 +980,21 @@
         <v>17</v>
       </c>
       <c r="D11" t="n">
-        <v>0.0000299935041140358</v>
+        <v>-0.000012169796241576</v>
       </c>
       <c r="E11" t="n">
-        <v>1.23908665610174</v>
+        <v>-0.414733170378454</v>
       </c>
       <c r="F11" t="n">
-        <v>0.225441810506541</v>
+        <v>0.681501483159199</v>
       </c>
       <c r="G11" t="n">
-        <v>0.795780330091566</v>
+        <v>0.937450214295248</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="B12" t="n">
         <v>15</v>
@@ -1055,62 +1003,16 @@
         <v>18</v>
       </c>
       <c r="D12" t="n">
-        <v>0.000014557262865104</v>
+        <v>-0.000032330399157212</v>
       </c>
       <c r="E12" t="n">
-        <v>0.589748316505002</v>
+        <v>-1.24295800102649</v>
       </c>
       <c r="F12" t="n">
-        <v>0.560015806497391</v>
+        <v>0.224203655099076</v>
       </c>
       <c r="G12" t="n">
-        <v>0.898701544885374</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="s">
-        <v>21</v>
-      </c>
-      <c r="B13" t="n">
-        <v>15</v>
-      </c>
-      <c r="C13" t="s">
-        <v>19</v>
-      </c>
-      <c r="D13" t="n">
-        <v>-0.0000131571838391805</v>
-      </c>
-      <c r="E13" t="n">
-        <v>-0.463673997735869</v>
-      </c>
-      <c r="F13" t="n">
-        <v>0.646410451407314</v>
-      </c>
-      <c r="G13" t="n">
-        <v>0.898701544885374</v>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="s">
-        <v>21</v>
-      </c>
-      <c r="B14" t="n">
-        <v>15</v>
-      </c>
-      <c r="C14" t="s">
-        <v>20</v>
-      </c>
-      <c r="D14" t="n">
-        <v>0.00000666033822352444</v>
-      </c>
-      <c r="E14" t="n">
-        <v>0.217242033014498</v>
-      </c>
-      <c r="F14" t="n">
-        <v>0.829570656817268</v>
-      </c>
-      <c r="G14" t="n">
-        <v>0.898701544885374</v>
+        <v>0.937450214295248</v>
       </c>
     </row>
   </sheetData>
@@ -1149,7 +1051,7 @@
     </row>
     <row r="2">
       <c r="A2" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="B2" t="n">
         <v>15</v>
@@ -1158,21 +1060,21 @@
         <v>8</v>
       </c>
       <c r="D2" t="n">
-        <v>0.0000294043784436642</v>
+        <v>0.00000872301305102348</v>
       </c>
       <c r="E2" t="n">
-        <v>0.89883001853054</v>
+        <v>0.283103004648163</v>
       </c>
       <c r="F2" t="n">
-        <v>0.376564337191749</v>
+        <v>0.779276959602381</v>
       </c>
       <c r="G2" t="n">
-        <v>0.708757155718691</v>
+        <v>0.88749309746541</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="B3" t="n">
         <v>15</v>
@@ -1181,21 +1083,21 @@
         <v>9</v>
       </c>
       <c r="D3" t="n">
-        <v>-0.00000629130888388581</v>
+        <v>0.0000148941534529123</v>
       </c>
       <c r="E3" t="n">
-        <v>-0.221365165866347</v>
+        <v>0.620235856073131</v>
       </c>
       <c r="F3" t="n">
-        <v>0.826447427446388</v>
+        <v>0.540350254464148</v>
       </c>
       <c r="G3" t="n">
-        <v>0.826447427446388</v>
+        <v>0.849121828443661</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="B4" t="n">
         <v>15</v>
@@ -1204,21 +1106,21 @@
         <v>10</v>
       </c>
       <c r="D4" t="n">
-        <v>-0.0000432728453534133</v>
+        <v>-0.00000435675783506388</v>
       </c>
       <c r="E4" t="n">
-        <v>-1.67101039032707</v>
+        <v>-0.142832101526431</v>
       </c>
       <c r="F4" t="n">
-        <v>0.106089702127298</v>
+        <v>0.88749309746541</v>
       </c>
       <c r="G4" t="n">
-        <v>0.689583063827438</v>
+        <v>0.88749309746541</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="B5" t="n">
         <v>15</v>
@@ -1227,21 +1129,21 @@
         <v>11</v>
       </c>
       <c r="D5" t="n">
-        <v>0.0000111589793869356</v>
+        <v>-0.0000283550587506986</v>
       </c>
       <c r="E5" t="n">
-        <v>0.494952014645566</v>
+        <v>-0.853445700266183</v>
       </c>
       <c r="F5" t="n">
-        <v>0.624574662360122</v>
+        <v>0.400989122954727</v>
       </c>
       <c r="G5" t="n">
-        <v>0.738133691880144</v>
+        <v>0.849121828443661</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="B6" t="n">
         <v>15</v>
@@ -1250,21 +1152,21 @@
         <v>12</v>
       </c>
       <c r="D6" t="n">
-        <v>-0.0000165251698390441</v>
+        <v>-0.0000197825844385406</v>
       </c>
       <c r="E6" t="n">
-        <v>-0.538604558851592</v>
+        <v>-0.627375435831817</v>
       </c>
       <c r="F6" t="n">
-        <v>0.594503251391765</v>
+        <v>0.535731461557543</v>
       </c>
       <c r="G6" t="n">
-        <v>0.738133691880144</v>
+        <v>0.849121828443661</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="B7" t="n">
         <v>15</v>
@@ -1273,21 +1175,21 @@
         <v>13</v>
       </c>
       <c r="D7" t="n">
-        <v>0.0000537327891602522</v>
+        <v>0.0000291476105123445</v>
       </c>
       <c r="E7" t="n">
-        <v>1.80618895858722</v>
+        <v>0.864562294089277</v>
       </c>
       <c r="F7" t="n">
-        <v>0.081871305670423</v>
+        <v>0.394965115722789</v>
       </c>
       <c r="G7" t="n">
-        <v>0.689583063827438</v>
+        <v>0.849121828443661</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="B8" t="n">
         <v>15</v>
@@ -1296,21 +1198,21 @@
         <v>14</v>
       </c>
       <c r="D8" t="n">
-        <v>0.0000308534283886261</v>
+        <v>0.0000321748531663511</v>
       </c>
       <c r="E8" t="n">
-        <v>1.03384511449983</v>
+        <v>1.14333627056156</v>
       </c>
       <c r="F8" t="n">
-        <v>0.310236001693465</v>
+        <v>0.2630271206213</v>
       </c>
       <c r="G8" t="n">
-        <v>0.708757155718691</v>
+        <v>0.849121828443661</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="B9" t="n">
         <v>15</v>
@@ -1319,21 +1221,21 @@
         <v>15</v>
       </c>
       <c r="D9" t="n">
-        <v>0.0000253219863875154</v>
+        <v>0.0000340751680228346</v>
       </c>
       <c r="E9" t="n">
-        <v>0.889176469974755</v>
+        <v>1.0307830174342</v>
       </c>
       <c r="F9" t="n">
-        <v>0.381638468463911</v>
+        <v>0.311871754205418</v>
       </c>
       <c r="G9" t="n">
-        <v>0.708757155718691</v>
+        <v>0.849121828443661</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="B10" t="n">
         <v>15</v>
@@ -1342,21 +1244,21 @@
         <v>16</v>
       </c>
       <c r="D10" t="n">
-        <v>-0.0000293293827052984</v>
+        <v>0.00000881146182536249</v>
       </c>
       <c r="E10" t="n">
-        <v>-0.907363491360261</v>
+        <v>0.243955563894828</v>
       </c>
       <c r="F10" t="n">
-        <v>0.372115691776949</v>
+        <v>0.809126373860497</v>
       </c>
       <c r="G10" t="n">
-        <v>0.708757155718691</v>
+        <v>0.88749309746541</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="B11" t="n">
         <v>15</v>
@@ -1365,21 +1267,21 @@
         <v>17</v>
       </c>
       <c r="D11" t="n">
-        <v>0.0000331512624471564</v>
+        <v>-0.000011086280640204</v>
       </c>
       <c r="E11" t="n">
-        <v>1.29614410224185</v>
+        <v>-0.354321987559795</v>
       </c>
       <c r="F11" t="n">
-        <v>0.205723485700145</v>
+        <v>0.725875164709554</v>
       </c>
       <c r="G11" t="n">
-        <v>0.708757155718691</v>
+        <v>0.88749309746541</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="B12" t="n">
         <v>15</v>
@@ -1388,62 +1290,16 @@
         <v>18</v>
       </c>
       <c r="D12" t="n">
-        <v>0.0000173694889819089</v>
+        <v>-0.0000423388892393826</v>
       </c>
       <c r="E12" t="n">
-        <v>0.664986695368876</v>
+        <v>-1.56258140839395</v>
       </c>
       <c r="F12" t="n">
-        <v>0.511610572788353</v>
+        <v>0.129903941896126</v>
       </c>
       <c r="G12" t="n">
-        <v>0.738133691880144</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="s">
-        <v>22</v>
-      </c>
-      <c r="B13" t="n">
-        <v>15</v>
-      </c>
-      <c r="C13" t="s">
-        <v>19</v>
-      </c>
-      <c r="D13" t="n">
-        <v>-0.000012170922226328</v>
-      </c>
-      <c r="E13" t="n">
-        <v>-0.401536852546754</v>
-      </c>
-      <c r="F13" t="n">
-        <v>0.691135550321308</v>
-      </c>
-      <c r="G13" t="n">
-        <v>0.74873017951475</v>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="s">
-        <v>22</v>
-      </c>
-      <c r="B14" t="n">
-        <v>15</v>
-      </c>
-      <c r="C14" t="s">
-        <v>20</v>
-      </c>
-      <c r="D14" t="n">
-        <v>0.0000183751102216709</v>
-      </c>
-      <c r="E14" t="n">
-        <v>0.562688872744356</v>
-      </c>
-      <c r="F14" t="n">
-        <v>0.57821615744296</v>
-      </c>
-      <c r="G14" t="n">
-        <v>0.738133691880144</v>
+        <v>0.849121828443661</v>
       </c>
     </row>
   </sheetData>
@@ -1482,7 +1338,7 @@
     </row>
     <row r="2">
       <c r="A2" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="B2" t="n">
         <v>15</v>
@@ -1491,21 +1347,21 @@
         <v>8</v>
       </c>
       <c r="D2" t="n">
-        <v>-0.0128315601881443</v>
+        <v>-0.0267014407257503</v>
       </c>
       <c r="E2" t="n">
-        <v>-0.518036324278407</v>
+        <v>-1.19426533391004</v>
       </c>
       <c r="F2" t="n">
-        <v>0.608841211241929</v>
+        <v>0.242511786003897</v>
       </c>
       <c r="G2" t="n">
-        <v>0.959485671896256</v>
+        <v>0.722499345396442</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="B3" t="n">
         <v>15</v>
@@ -1514,21 +1370,21 @@
         <v>9</v>
       </c>
       <c r="D3" t="n">
-        <v>-0.00673616146818887</v>
+        <v>0.0150993555873671</v>
       </c>
       <c r="E3" t="n">
-        <v>-0.319286500804686</v>
+        <v>0.84457898555314</v>
       </c>
       <c r="F3" t="n">
-        <v>0.75207671835784</v>
+        <v>0.40558934833529</v>
       </c>
       <c r="G3" t="n">
-        <v>0.959485671896256</v>
+        <v>0.722499345396442</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="B4" t="n">
         <v>15</v>
@@ -1537,21 +1393,21 @@
         <v>10</v>
       </c>
       <c r="D4" t="n">
-        <v>0.0158313090248825</v>
+        <v>0.00714726934407565</v>
       </c>
       <c r="E4" t="n">
-        <v>0.79597708721575</v>
+        <v>0.315734011229177</v>
       </c>
       <c r="F4" t="n">
-        <v>0.433298812431082</v>
+        <v>0.754573604931762</v>
       </c>
       <c r="G4" t="n">
-        <v>0.804697794514866</v>
+        <v>0.830030965424939</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="B5" t="n">
         <v>15</v>
@@ -1560,21 +1416,21 @@
         <v>11</v>
       </c>
       <c r="D5" t="n">
-        <v>0.0142707921642979</v>
+        <v>0.0422020906301423</v>
       </c>
       <c r="E5" t="n">
-        <v>0.878796012733284</v>
+        <v>1.78477625293328</v>
       </c>
       <c r="F5" t="n">
-        <v>0.387612558501802</v>
+        <v>0.0852663763545763</v>
       </c>
       <c r="G5" t="n">
-        <v>0.804697794514866</v>
+        <v>0.722499345396442</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="B6" t="n">
         <v>15</v>
@@ -1583,21 +1439,21 @@
         <v>12</v>
       </c>
       <c r="D6" t="n">
-        <v>-0.0322225384106675</v>
+        <v>-0.0332470580657915</v>
       </c>
       <c r="E6" t="n">
-        <v>-1.45455876814791</v>
+        <v>-1.46330208389789</v>
       </c>
       <c r="F6" t="n">
-        <v>0.157834320001481</v>
+        <v>0.154652549594345</v>
       </c>
       <c r="G6" t="n">
-        <v>0.508059007192624</v>
+        <v>0.722499345396442</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="B7" t="n">
         <v>15</v>
@@ -1606,21 +1462,21 @@
         <v>13</v>
       </c>
       <c r="D7" t="n">
-        <v>0.0013834415619434</v>
+        <v>-0.0143503187143016</v>
       </c>
       <c r="E7" t="n">
-        <v>0.0587821575691948</v>
+        <v>-0.569654615023426</v>
       </c>
       <c r="F7" t="n">
-        <v>0.953577948807204</v>
+        <v>0.573508124094988</v>
       </c>
       <c r="G7" t="n">
-        <v>0.959485671896256</v>
+        <v>0.722499345396442</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="B8" t="n">
         <v>15</v>
@@ -1629,21 +1485,21 @@
         <v>14</v>
       </c>
       <c r="D8" t="n">
-        <v>-0.0321390234508986</v>
+        <v>-0.0201736114912111</v>
       </c>
       <c r="E8" t="n">
-        <v>-1.47372984801834</v>
+        <v>-0.955836149738617</v>
       </c>
       <c r="F8" t="n">
-        <v>0.152635705286899</v>
+        <v>0.347431904278243</v>
       </c>
       <c r="G8" t="n">
-        <v>0.508059007192624</v>
+        <v>0.722499345396442</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="B9" t="n">
         <v>15</v>
@@ -1652,21 +1508,21 @@
         <v>15</v>
       </c>
       <c r="D9" t="n">
-        <v>-0.0276333192861384</v>
+        <v>-0.0272305460849128</v>
       </c>
       <c r="E9" t="n">
-        <v>-1.32918250710847</v>
+        <v>-1.11361309401611</v>
       </c>
       <c r="F9" t="n">
-        <v>0.195407310458701</v>
+        <v>0.275025665524663</v>
       </c>
       <c r="G9" t="n">
-        <v>0.508059007192624</v>
+        <v>0.722499345396442</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="B10" t="n">
         <v>15</v>
@@ -1675,21 +1531,21 @@
         <v>16</v>
       </c>
       <c r="D10" t="n">
-        <v>0.0430127255563795</v>
+        <v>0.0144758465052967</v>
       </c>
       <c r="E10" t="n">
-        <v>1.86276544457451</v>
+        <v>0.543502991590459</v>
       </c>
       <c r="F10" t="n">
-        <v>0.0739039904885873</v>
+        <v>0.591135828051634</v>
       </c>
       <c r="G10" t="n">
-        <v>0.508059007192624</v>
+        <v>0.722499345396442</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="B11" t="n">
         <v>15</v>
@@ -1698,21 +1554,21 @@
         <v>17</v>
       </c>
       <c r="D11" t="n">
-        <v>-0.0016377172426531</v>
+        <v>-0.000750809886064641</v>
       </c>
       <c r="E11" t="n">
-        <v>-0.0841488202866328</v>
+        <v>-0.0322349446149444</v>
       </c>
       <c r="F11" t="n">
-        <v>0.933586789706812</v>
+        <v>0.97451608722466</v>
       </c>
       <c r="G11" t="n">
-        <v>0.959485671896256</v>
+        <v>0.97451608722466</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="B12" t="n">
         <v>15</v>
@@ -1721,62 +1577,16 @@
         <v>18</v>
       </c>
       <c r="D12" t="n">
-        <v>0.0305797145608455</v>
+        <v>0.014549789311815</v>
       </c>
       <c r="E12" t="n">
-        <v>1.65330786065693</v>
+        <v>0.696291503477936</v>
       </c>
       <c r="F12" t="n">
-        <v>0.110370537772024</v>
+        <v>0.492054240955837</v>
       </c>
       <c r="G12" t="n">
-        <v>0.508059007192624</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="s">
-        <v>23</v>
-      </c>
-      <c r="B13" t="n">
-        <v>15</v>
-      </c>
-      <c r="C13" t="s">
-        <v>19</v>
-      </c>
-      <c r="D13" t="n">
-        <v>-0.0016438805052348</v>
-      </c>
-      <c r="E13" t="n">
-        <v>-0.072454405147162</v>
-      </c>
-      <c r="F13" t="n">
-        <v>0.942798319103128</v>
-      </c>
-      <c r="G13" t="n">
-        <v>0.959485671896256</v>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="s">
-        <v>23</v>
-      </c>
-      <c r="B14" t="n">
-        <v>15</v>
-      </c>
-      <c r="C14" t="s">
-        <v>20</v>
-      </c>
-      <c r="D14" t="n">
-        <v>0.00126295692156176</v>
-      </c>
-      <c r="E14" t="n">
-        <v>0.0512941570489743</v>
-      </c>
-      <c r="F14" t="n">
-        <v>0.959485671896256</v>
-      </c>
-      <c r="G14" t="n">
-        <v>0.959485671896256</v>
+        <v>0.722499345396442</v>
       </c>
     </row>
   </sheetData>
@@ -1815,7 +1625,7 @@
     </row>
     <row r="2">
       <c r="A2" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="B2" t="n">
         <v>15</v>
@@ -1824,21 +1634,21 @@
         <v>8</v>
       </c>
       <c r="D2" t="n">
-        <v>0.00166040047749804</v>
+        <v>0.00209142764210136</v>
       </c>
       <c r="E2" t="n">
-        <v>1.22468749833325</v>
+        <v>1.67673290266403</v>
       </c>
       <c r="F2" t="n">
-        <v>0.229575953966727</v>
+        <v>0.10331964187004</v>
       </c>
       <c r="G2" t="n">
-        <v>0.634755103491085</v>
+        <v>0.387672008291873</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="B3" t="n">
         <v>15</v>
@@ -1847,21 +1657,21 @@
         <v>9</v>
       </c>
       <c r="D3" t="n">
-        <v>0.000947038403419778</v>
+        <v>0.000153147749281699</v>
       </c>
       <c r="E3" t="n">
-        <v>0.787640654821504</v>
+        <v>0.14356429662774</v>
       </c>
       <c r="F3" t="n">
-        <v>0.436665899158292</v>
+        <v>0.886743030818968</v>
       </c>
       <c r="G3" t="n">
-        <v>0.709582086132224</v>
+        <v>0.960344277052755</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="B4" t="n">
         <v>15</v>
@@ -1870,21 +1680,21 @@
         <v>10</v>
       </c>
       <c r="D4" t="n">
-        <v>-0.00121282636712334</v>
+        <v>-0.0000645699392410471</v>
       </c>
       <c r="E4" t="n">
-        <v>-1.05575103268835</v>
+        <v>-0.0501116697454154</v>
       </c>
       <c r="F4" t="n">
-        <v>0.298938005173393</v>
+        <v>0.960344277052755</v>
       </c>
       <c r="G4" t="n">
-        <v>0.634755103491085</v>
+        <v>0.960344277052755</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="B5" t="n">
         <v>15</v>
@@ -1893,21 +1703,21 @@
         <v>11</v>
       </c>
       <c r="D5" t="n">
-        <v>-0.0000461346381067309</v>
+        <v>-0.00265646273613031</v>
       </c>
       <c r="E5" t="n">
-        <v>-0.0457360619039802</v>
+        <v>-2.01043057431603</v>
       </c>
       <c r="F5" t="n">
-        <v>0.963803053053092</v>
+        <v>0.0528598312354243</v>
       </c>
       <c r="G5" t="n">
-        <v>0.963803053053092</v>
+        <v>0.387672008291873</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="B6" t="n">
         <v>15</v>
@@ -1916,21 +1726,21 @@
         <v>12</v>
       </c>
       <c r="D6" t="n">
-        <v>0.00221036585987631</v>
+        <v>0.00212933811752087</v>
       </c>
       <c r="E6" t="n">
-        <v>1.78083838066294</v>
+        <v>1.66463876966785</v>
       </c>
       <c r="F6" t="n">
-        <v>0.0843743703807095</v>
+        <v>0.105728729534147</v>
       </c>
       <c r="G6" t="n">
-        <v>0.548433407474612</v>
+        <v>0.387672008291873</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="B7" t="n">
         <v>15</v>
@@ -1939,21 +1749,21 @@
         <v>13</v>
       </c>
       <c r="D7" t="n">
-        <v>0.000142847080932194</v>
+        <v>0.00167623029345924</v>
       </c>
       <c r="E7" t="n">
-        <v>0.107933871914545</v>
+        <v>1.20646811570144</v>
       </c>
       <c r="F7" t="n">
-        <v>0.914717801560134</v>
+        <v>0.236463667194653</v>
       </c>
       <c r="G7" t="n">
-        <v>0.963803053053092</v>
+        <v>0.520220067828237</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="B8" t="n">
         <v>15</v>
@@ -1962,21 +1772,21 @@
         <v>14</v>
       </c>
       <c r="D8" t="n">
-        <v>0.00122273241104637</v>
+        <v>0.00158872729182738</v>
       </c>
       <c r="E8" t="n">
-        <v>0.964887534118042</v>
+        <v>1.32845295732855</v>
       </c>
       <c r="F8" t="n">
-        <v>0.341791209572123</v>
+        <v>0.193406838760615</v>
       </c>
       <c r="G8" t="n">
-        <v>0.634755103491085</v>
+        <v>0.520220067828237</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="B9" t="n">
         <v>15</v>
@@ -1985,21 +1795,21 @@
         <v>15</v>
       </c>
       <c r="D9" t="n">
-        <v>0.00158053222655899</v>
+        <v>0.000880597923807462</v>
       </c>
       <c r="E9" t="n">
-        <v>1.31951219549919</v>
+        <v>0.631368495717466</v>
       </c>
       <c r="F9" t="n">
-        <v>0.196302221254155</v>
+        <v>0.532275248070096</v>
       </c>
       <c r="G9" t="n">
-        <v>0.634755103491085</v>
+        <v>0.731878466096382</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="B10" t="n">
         <v>15</v>
@@ -2008,21 +1818,21 @@
         <v>16</v>
       </c>
       <c r="D10" t="n">
-        <v>-0.0026987451844382</v>
+        <v>-0.000987041670795646</v>
       </c>
       <c r="E10" t="n">
-        <v>-2.09572564674176</v>
+        <v>-0.665876945609607</v>
       </c>
       <c r="F10" t="n">
-        <v>0.0440524217217588</v>
+        <v>0.510252323017137</v>
       </c>
       <c r="G10" t="n">
-        <v>0.548433407474612</v>
+        <v>0.731878466096382</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="B11" t="n">
         <v>15</v>
@@ -2031,21 +1841,21 @@
         <v>17</v>
       </c>
       <c r="D11" t="n">
-        <v>0.00110612261301509</v>
+        <v>-0.000305801545536374</v>
       </c>
       <c r="E11" t="n">
-        <v>0.985921471081764</v>
+        <v>-0.232057183911123</v>
       </c>
       <c r="F11" t="n">
-        <v>0.33152136807187</v>
+        <v>0.817968364751842</v>
       </c>
       <c r="G11" t="n">
-        <v>0.634755103491085</v>
+        <v>0.960344277052755</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="B12" t="n">
         <v>15</v>
@@ -2054,62 +1864,16 @@
         <v>18</v>
       </c>
       <c r="D12" t="n">
-        <v>0.000173554401354102</v>
+        <v>-0.0011252670458588</v>
       </c>
       <c r="E12" t="n">
-        <v>0.152555000649706</v>
+        <v>-0.942621387434086</v>
       </c>
       <c r="F12" t="n">
-        <v>0.879701006879189</v>
+        <v>0.352923292680626</v>
       </c>
       <c r="G12" t="n">
-        <v>0.963803053053092</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="s">
-        <v>24</v>
-      </c>
-      <c r="B13" t="n">
-        <v>15</v>
-      </c>
-      <c r="C13" t="s">
-        <v>19</v>
-      </c>
-      <c r="D13" t="n">
-        <v>-0.000292112642518584</v>
-      </c>
-      <c r="E13" t="n">
-        <v>-0.227559084719827</v>
-      </c>
-      <c r="F13" t="n">
-        <v>0.821427557507584</v>
-      </c>
-      <c r="G13" t="n">
-        <v>0.963803053053092</v>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="s">
-        <v>24</v>
-      </c>
-      <c r="B14" t="n">
-        <v>15</v>
-      </c>
-      <c r="C14" t="s">
-        <v>20</v>
-      </c>
-      <c r="D14" t="n">
-        <v>-0.000417899246002439</v>
-      </c>
-      <c r="E14" t="n">
-        <v>-0.304549361996843</v>
-      </c>
-      <c r="F14" t="n">
-        <v>0.762668787063112</v>
-      </c>
-      <c r="G14" t="n">
-        <v>0.963803053053092</v>
+        <v>0.647026036581148</v>
       </c>
     </row>
   </sheetData>
@@ -2148,7 +1912,7 @@
     </row>
     <row r="2">
       <c r="A2" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="B2" t="n">
         <v>14</v>
@@ -2157,21 +1921,21 @@
         <v>8</v>
       </c>
       <c r="D2" t="n">
-        <v>0.00537473925204176</v>
+        <v>0.00159952389165491</v>
       </c>
       <c r="E2" t="n">
-        <v>0.682028256900366</v>
+        <v>0.22915581814018</v>
       </c>
       <c r="F2" t="n">
-        <v>0.500366757935589</v>
+        <v>0.819618352295196</v>
       </c>
       <c r="G2" t="n">
-        <v>0.693805919984501</v>
+        <v>0.901580187524715</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="B3" t="n">
         <v>14</v>
@@ -2180,21 +1944,21 @@
         <v>9</v>
       </c>
       <c r="D3" t="n">
-        <v>0.0038109961451836</v>
+        <v>0.00340885814815899</v>
       </c>
       <c r="E3" t="n">
-        <v>0.629517174736605</v>
+        <v>0.524736206906375</v>
       </c>
       <c r="F3" t="n">
-        <v>0.533696861526539</v>
+        <v>0.601926250462226</v>
       </c>
       <c r="G3" t="n">
-        <v>0.693805919984501</v>
+        <v>0.827648594385561</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="B4" t="n">
         <v>14</v>
@@ -2203,21 +1967,21 @@
         <v>10</v>
       </c>
       <c r="D4" t="n">
-        <v>0.000183276989156598</v>
+        <v>0.00744618506140498</v>
       </c>
       <c r="E4" t="n">
-        <v>0.0275896903764297</v>
+        <v>1.09463062200014</v>
       </c>
       <c r="F4" t="n">
-        <v>0.978169092911676</v>
+        <v>0.278564116795406</v>
       </c>
       <c r="G4" t="n">
-        <v>0.978169092911676</v>
+        <v>0.612841056949893</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="B5" t="n">
         <v>14</v>
@@ -2226,21 +1990,21 @@
         <v>11</v>
       </c>
       <c r="D5" t="n">
-        <v>0.0023320680118407</v>
+        <v>0.00466248524303698</v>
       </c>
       <c r="E5" t="n">
-        <v>0.416546221984151</v>
+        <v>0.632780585621648</v>
       </c>
       <c r="F5" t="n">
-        <v>0.679926545971349</v>
+        <v>0.529562424135087</v>
       </c>
       <c r="G5" t="n">
-        <v>0.803549554329776</v>
+        <v>0.827648594385561</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="B6" t="n">
         <v>14</v>
@@ -2249,21 +2013,21 @@
         <v>12</v>
       </c>
       <c r="D6" t="n">
-        <v>-0.0121199962564611</v>
+        <v>-0.0119290792668818</v>
       </c>
       <c r="E6" t="n">
-        <v>-1.75738235006888</v>
+        <v>-1.6728426736799</v>
       </c>
       <c r="F6" t="n">
-        <v>0.088884916700752</v>
+        <v>0.100175172737007</v>
       </c>
       <c r="G6" t="n">
-        <v>0.288875979277444</v>
+        <v>0.367308966702358</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="B7" t="n">
         <v>14</v>
@@ -2272,21 +2036,21 @@
         <v>13</v>
       </c>
       <c r="D7" t="n">
-        <v>0.0139184417511595</v>
+        <v>0.00544754815708406</v>
       </c>
       <c r="E7" t="n">
-        <v>1.94630519758492</v>
+        <v>0.708966995718737</v>
       </c>
       <c r="F7" t="n">
-        <v>0.0608788418458501</v>
+        <v>0.48141170224623</v>
       </c>
       <c r="G7" t="n">
-        <v>0.26380831466535</v>
+        <v>0.827648594385561</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="B8" t="n">
         <v>14</v>
@@ -2295,21 +2059,21 @@
         <v>14</v>
       </c>
       <c r="D8" t="n">
-        <v>0.0073963381357885</v>
+        <v>-0.000874793580008837</v>
       </c>
       <c r="E8" t="n">
-        <v>1.08192113888604</v>
+        <v>-0.123859469807284</v>
       </c>
       <c r="F8" t="n">
-        <v>0.28776556047406</v>
+        <v>0.901889002389484</v>
       </c>
       <c r="G8" t="n">
-        <v>0.693805919984501</v>
+        <v>0.901889002389484</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="B9" t="n">
         <v>14</v>
@@ -2318,21 +2082,21 @@
         <v>15</v>
       </c>
       <c r="D9" t="n">
-        <v>-0.00145335839069196</v>
+        <v>0.00971093611510755</v>
       </c>
       <c r="E9" t="n">
-        <v>-0.206977825214634</v>
+        <v>1.33193019078791</v>
       </c>
       <c r="F9" t="n">
-        <v>0.837402466513032</v>
+        <v>0.188508853359351</v>
       </c>
       <c r="G9" t="n">
-        <v>0.907186005389118</v>
+        <v>0.518399346738216</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="B10" t="n">
         <v>14</v>
@@ -2341,21 +2105,21 @@
         <v>16</v>
       </c>
       <c r="D10" t="n">
-        <v>0.0050027058155605</v>
+        <v>0.0192854241630728</v>
       </c>
       <c r="E10" t="n">
-        <v>0.677338654876542</v>
+        <v>2.63683894850152</v>
       </c>
       <c r="F10" t="n">
-        <v>0.503295564169081</v>
+        <v>0.0109202174795317</v>
       </c>
       <c r="G10" t="n">
-        <v>0.693805919984501</v>
+        <v>0.120122392274849</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="B11" t="n">
         <v>14</v>
@@ -2364,21 +2128,21 @@
         <v>17</v>
       </c>
       <c r="D11" t="n">
-        <v>-0.00473709531556869</v>
+        <v>-0.0132952701168567</v>
       </c>
       <c r="E11" t="n">
-        <v>-0.741515093154228</v>
+        <v>-1.94576130877082</v>
       </c>
       <c r="F11" t="n">
-        <v>0.464051471803836</v>
+        <v>0.0569253257498476</v>
       </c>
       <c r="G11" t="n">
-        <v>0.693805919984501</v>
+        <v>0.313089291624162</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="B12" t="n">
         <v>14</v>
@@ -2387,62 +2151,16 @@
         <v>18</v>
       </c>
       <c r="D12" t="n">
-        <v>0.0047537775063885</v>
+        <v>-0.0028053631365646</v>
       </c>
       <c r="E12" t="n">
-        <v>0.809863144735917</v>
+        <v>-0.400927913985043</v>
       </c>
       <c r="F12" t="n">
-        <v>0.424290910938905</v>
+        <v>0.690064053576938</v>
       </c>
       <c r="G12" t="n">
-        <v>0.693805919984501</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="s">
-        <v>25</v>
-      </c>
-      <c r="B13" t="n">
-        <v>14</v>
-      </c>
-      <c r="C13" t="s">
-        <v>19</v>
-      </c>
-      <c r="D13" t="n">
-        <v>-0.0134125882941576</v>
-      </c>
-      <c r="E13" t="n">
-        <v>-2.1053528328679</v>
-      </c>
-      <c r="F13" t="n">
-        <v>0.0435955830455525</v>
-      </c>
-      <c r="G13" t="n">
-        <v>0.26380831466535</v>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="s">
-        <v>25</v>
-      </c>
-      <c r="B14" t="n">
-        <v>14</v>
-      </c>
-      <c r="C14" t="s">
-        <v>20</v>
-      </c>
-      <c r="D14" t="n">
-        <v>0.0161828883105628</v>
-      </c>
-      <c r="E14" t="n">
-        <v>2.36841006682896</v>
-      </c>
-      <c r="F14" t="n">
-        <v>0.0243885556579516</v>
-      </c>
-      <c r="G14" t="n">
-        <v>0.26380831466535</v>
+        <v>0.84341162103848</v>
       </c>
     </row>
   </sheetData>
@@ -2481,7 +2199,7 @@
     </row>
     <row r="2">
       <c r="A2" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="B2" t="n">
         <v>15</v>
@@ -2490,21 +2208,21 @@
         <v>8</v>
       </c>
       <c r="D2" t="n">
-        <v>0.0628402129650179</v>
+        <v>-0.0850967711531811</v>
       </c>
       <c r="E2" t="n">
-        <v>0.71060503979183</v>
+        <v>-1.04792188874735</v>
       </c>
       <c r="F2" t="n">
-        <v>0.483465808155231</v>
+        <v>0.303526043559196</v>
       </c>
       <c r="G2" t="n">
-        <v>0.736577922426124</v>
+        <v>0.84865038111329</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="B3" t="n">
         <v>15</v>
@@ -2513,21 +2231,21 @@
         <v>9</v>
       </c>
       <c r="D3" t="n">
-        <v>-0.0835227486753506</v>
+        <v>0.0399796683978149</v>
       </c>
       <c r="E3" t="n">
-        <v>-1.11830133640729</v>
+        <v>0.607650138296825</v>
       </c>
       <c r="F3" t="n">
-        <v>0.273359624730614</v>
+        <v>0.548256132146037</v>
       </c>
       <c r="G3" t="n">
-        <v>0.736577922426124</v>
+        <v>0.84865038111329</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="B4" t="n">
         <v>15</v>
@@ -2536,21 +2254,21 @@
         <v>10</v>
       </c>
       <c r="D4" t="n">
-        <v>-0.0508877563674896</v>
+        <v>-0.0514811216103741</v>
       </c>
       <c r="E4" t="n">
-        <v>-0.703648658196014</v>
+        <v>-0.632990739098653</v>
       </c>
       <c r="F4" t="n">
-        <v>0.487718671761893</v>
+        <v>0.531812474519359</v>
       </c>
       <c r="G4" t="n">
-        <v>0.736577922426124</v>
+        <v>0.84865038111329</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="B5" t="n">
         <v>15</v>
@@ -2559,21 +2277,21 @@
         <v>11</v>
       </c>
       <c r="D5" t="n">
-        <v>0.0401909135880194</v>
+        <v>0.0681530650268026</v>
       </c>
       <c r="E5" t="n">
-        <v>0.667849968645065</v>
+        <v>0.766545320745093</v>
       </c>
       <c r="F5" t="n">
-        <v>0.509938561679624</v>
+        <v>0.44968765994241</v>
       </c>
       <c r="G5" t="n">
-        <v>0.736577922426124</v>
+        <v>0.84865038111329</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="B6" t="n">
         <v>15</v>
@@ -2582,21 +2300,21 @@
         <v>12</v>
       </c>
       <c r="D6" t="n">
-        <v>-0.0913539481500175</v>
+        <v>-0.102016648999199</v>
       </c>
       <c r="E6" t="n">
-        <v>-1.12778229936861</v>
+        <v>-1.23144584892888</v>
       </c>
       <c r="F6" t="n">
-        <v>0.269404710312093</v>
+        <v>0.228273103486154</v>
       </c>
       <c r="G6" t="n">
-        <v>0.736577922426124</v>
+        <v>0.84865038111329</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="B7" t="n">
         <v>15</v>
@@ -2605,21 +2323,21 @@
         <v>13</v>
       </c>
       <c r="D7" t="n">
-        <v>0.0624738227193752</v>
+        <v>0.0579820359273812</v>
       </c>
       <c r="E7" t="n">
-        <v>0.746135903943166</v>
+        <v>0.641031013254417</v>
       </c>
       <c r="F7" t="n">
-        <v>0.462078554484262</v>
+        <v>0.526650619320487</v>
       </c>
       <c r="G7" t="n">
-        <v>0.736577922426124</v>
+        <v>0.84865038111329</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="B8" t="n">
         <v>15</v>
@@ -2628,21 +2346,21 @@
         <v>14</v>
       </c>
       <c r="D8" t="n">
-        <v>-0.0313557900854947</v>
+        <v>0.0228293539600817</v>
       </c>
       <c r="E8" t="n">
-        <v>-0.384594324559212</v>
+        <v>0.294350529814585</v>
       </c>
       <c r="F8" t="n">
-        <v>0.7035721218581</v>
+        <v>0.770634414407294</v>
       </c>
       <c r="G8" t="n">
-        <v>0.846070264705897</v>
+        <v>0.84865038111329</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="B9" t="n">
         <v>15</v>
@@ -2651,21 +2369,21 @@
         <v>15</v>
       </c>
       <c r="D9" t="n">
-        <v>0.00169794430724057</v>
+        <v>-0.025615293492557</v>
       </c>
       <c r="E9" t="n">
-        <v>0.0218808539112619</v>
+        <v>-0.285301937159728</v>
       </c>
       <c r="F9" t="n">
-        <v>0.982705050330138</v>
+        <v>0.777486700273011</v>
       </c>
       <c r="G9" t="n">
-        <v>0.982705050330138</v>
+        <v>0.84865038111329</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="B10" t="n">
         <v>15</v>
@@ -2674,21 +2392,21 @@
         <v>16</v>
       </c>
       <c r="D10" t="n">
-        <v>0.0660173187060582</v>
+        <v>-0.0184944276531132</v>
       </c>
       <c r="E10" t="n">
-        <v>0.756324302434523</v>
+        <v>-0.192593317505326</v>
       </c>
       <c r="F10" t="n">
-        <v>0.456050209087962</v>
+        <v>0.84865038111329</v>
       </c>
       <c r="G10" t="n">
-        <v>0.736577922426124</v>
+        <v>0.84865038111329</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="B11" t="n">
         <v>15</v>
@@ -2697,21 +2415,21 @@
         <v>17</v>
       </c>
       <c r="D11" t="n">
-        <v>0.0499340985904864</v>
+        <v>0.0338867052011082</v>
       </c>
       <c r="E11" t="n">
-        <v>0.71269607470873</v>
+        <v>0.404459850497136</v>
       </c>
       <c r="F11" t="n">
-        <v>0.482191599116647</v>
+        <v>0.68890968172982</v>
       </c>
       <c r="G11" t="n">
-        <v>0.736577922426124</v>
+        <v>0.84865038111329</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="B12" t="n">
         <v>15</v>
@@ -2720,62 +2438,16 @@
         <v>18</v>
       </c>
       <c r="D12" t="n">
-        <v>0.0643570684237117</v>
+        <v>-0.0430462035637821</v>
       </c>
       <c r="E12" t="n">
-        <v>0.925038001655114</v>
+        <v>-0.566657525265147</v>
       </c>
       <c r="F12" t="n">
-        <v>0.363198699876998</v>
+        <v>0.575405721000864</v>
       </c>
       <c r="G12" t="n">
-        <v>0.736577922426124</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="s">
-        <v>26</v>
-      </c>
-      <c r="B13" t="n">
-        <v>15</v>
-      </c>
-      <c r="C13" t="s">
-        <v>19</v>
-      </c>
-      <c r="D13" t="n">
-        <v>0.0299748908304498</v>
-      </c>
-      <c r="E13" t="n">
-        <v>0.367806516620173</v>
-      </c>
-      <c r="F13" t="n">
-        <v>0.715905608597297</v>
-      </c>
-      <c r="G13" t="n">
-        <v>0.846070264705897</v>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="s">
-        <v>26</v>
-      </c>
-      <c r="B14" t="n">
-        <v>15</v>
-      </c>
-      <c r="C14" t="s">
-        <v>20</v>
-      </c>
-      <c r="D14" t="n">
-        <v>-0.0189689418657309</v>
-      </c>
-      <c r="E14" t="n">
-        <v>-0.214965134972093</v>
-      </c>
-      <c r="F14" t="n">
-        <v>0.831421456659421</v>
-      </c>
-      <c r="G14" t="n">
-        <v>0.900706578047706</v>
+        <v>0.84865038111329</v>
       </c>
     </row>
   </sheetData>
@@ -2791,45 +2463,45 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="s">
+        <v>25</v>
+      </c>
+      <c r="B1" t="s">
+        <v>26</v>
+      </c>
+      <c r="C1" t="s">
         <v>27</v>
-      </c>
-      <c r="B1" t="s">
-        <v>28</v>
-      </c>
-      <c r="C1" t="s">
-        <v>29</v>
       </c>
       <c r="D1" t="s">
         <v>0</v>
       </c>
       <c r="E1" t="s">
+        <v>28</v>
+      </c>
+      <c r="F1" t="s">
+        <v>29</v>
+      </c>
+      <c r="G1" t="s">
         <v>30</v>
       </c>
-      <c r="F1" t="s">
+      <c r="H1" t="s">
         <v>31</v>
-      </c>
-      <c r="G1" t="s">
-        <v>32</v>
-      </c>
-      <c r="H1" t="s">
-        <v>33</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="s">
+        <v>32</v>
+      </c>
+      <c r="B2" t="s">
+        <v>33</v>
+      </c>
+      <c r="C2" t="s">
         <v>34</v>
-      </c>
-      <c r="B2" t="s">
-        <v>35</v>
-      </c>
-      <c r="C2" t="s">
-        <v>36</v>
       </c>
       <c r="D2" t="s">
         <v>7</v>
       </c>
       <c r="E2" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="F2" t="n">
         <v>0</v>
@@ -2838,76 +2510,76 @@
         <v>0</v>
       </c>
       <c r="H2" t="n">
-        <v>0.00290840880033159</v>
+        <v>0.00262746819273299</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="s">
+        <v>32</v>
+      </c>
+      <c r="B3" t="s">
+        <v>33</v>
+      </c>
+      <c r="C3" t="s">
         <v>34</v>
       </c>
-      <c r="B3" t="s">
-        <v>35</v>
-      </c>
-      <c r="C3" t="s">
-        <v>36</v>
-      </c>
       <c r="D3" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="E3" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="F3" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G3" t="n">
         <v>0</v>
       </c>
       <c r="H3" t="n">
-        <v>0.0050027058155605</v>
+        <v>0.00544754815708406</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="s">
+        <v>32</v>
+      </c>
+      <c r="B4" t="s">
+        <v>33</v>
+      </c>
+      <c r="C4" t="s">
         <v>34</v>
       </c>
-      <c r="B4" t="s">
-        <v>35</v>
-      </c>
-      <c r="C4" t="s">
-        <v>36</v>
-      </c>
       <c r="D4" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="E4" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="F4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G4" t="n">
         <v>0</v>
       </c>
       <c r="H4" t="n">
-        <v>0.00110612261301509</v>
+        <v>0.0011252670458588</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="s">
+        <v>32</v>
+      </c>
+      <c r="B5" t="s">
+        <v>33</v>
+      </c>
+      <c r="C5" t="s">
         <v>34</v>
       </c>
-      <c r="B5" t="s">
-        <v>35</v>
-      </c>
-      <c r="C5" t="s">
-        <v>36</v>
-      </c>
       <c r="D5" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="E5" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="F5" t="n">
         <v>0</v>
@@ -2916,24 +2588,24 @@
         <v>0</v>
       </c>
       <c r="H5" t="n">
-        <v>0.000017230061084906</v>
+        <v>0.000012169796241576</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="s">
+        <v>32</v>
+      </c>
+      <c r="B6" t="s">
+        <v>33</v>
+      </c>
+      <c r="C6" t="s">
         <v>34</v>
       </c>
-      <c r="B6" t="s">
-        <v>35</v>
-      </c>
-      <c r="C6" t="s">
-        <v>36</v>
-      </c>
       <c r="D6" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="E6" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="F6" t="n">
         <v>0</v>
@@ -2942,24 +2614,24 @@
         <v>0</v>
       </c>
       <c r="H6" t="n">
-        <v>0.0000253219863875154</v>
+        <v>0.0000197825844385406</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="s">
+        <v>32</v>
+      </c>
+      <c r="B7" t="s">
+        <v>33</v>
+      </c>
+      <c r="C7" t="s">
         <v>34</v>
       </c>
-      <c r="B7" t="s">
-        <v>35</v>
-      </c>
-      <c r="C7" t="s">
-        <v>36</v>
-      </c>
       <c r="D7" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="E7" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="F7" t="n">
         <v>0</v>
@@ -2968,24 +2640,24 @@
         <v>0</v>
       </c>
       <c r="H7" t="n">
-        <v>0.0142707921642979</v>
+        <v>0.0150993555873671</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="s">
+        <v>32</v>
+      </c>
+      <c r="B8" t="s">
+        <v>33</v>
+      </c>
+      <c r="C8" t="s">
         <v>34</v>
       </c>
-      <c r="B8" t="s">
-        <v>35</v>
-      </c>
-      <c r="C8" t="s">
-        <v>36</v>
-      </c>
       <c r="D8" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="E8" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="F8" t="n">
         <v>0</v>
@@ -2994,7 +2666,7 @@
         <v>0</v>
       </c>
       <c r="H8" t="n">
-        <v>0.0508877563674896</v>
+        <v>0.0430462035637821</v>
       </c>
     </row>
   </sheetData>
